--- a/space-battleship/config_excel/hightech.xlsx
+++ b/space-battleship/config_excel/hightech.xlsx
@@ -2,17 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\放置\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="0" firstSheet="0"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="hightech" sheetId="8" r:id="rId8" state="visible"/>
+    <sheet name="hightech" sheetId="8" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,524 +27,56 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="181">
-  <si>
-    <t>太空战舰是一个科幻飞行器不断攻击敌方飞行器的小游戏，横版，即时，有相关画面。玩家不需操作</t>
-  </si>
-  <si>
-    <t>战舰会自动使用武器，攻击敌方飞行器，武器有各种参数，在武器表里定义</t>
-  </si>
-  <si>
-    <t>在每个关卡，敌方飞行器每隔一段距离就会出现。全部击落后才能前进，战斗时无法移动。关卡最后出现一个敌方BOSS飞行器，击毁后通关</t>
-  </si>
-  <si>
-    <t>敌方飞行器有各种参数，在怪物表里配置。怪物群负责整理一整群怪物，而关卡表将配置怪物群，用来辨别哪些敌方飞行器将出现在关卡里及出现在关卡的什么位置</t>
-  </si>
-  <si>
-    <t>敌方飞行器被击毁后会掉落资源，鼠标划过可以拾取。如果一段时间没有拾取，则自动拾取，但会有损耗，损耗比例在config里配置</t>
-  </si>
-  <si>
-    <t>飞行器初始武器为激光，激光会发射一道光束，攻击一个目标。</t>
-  </si>
-  <si>
-    <t>第二个武器为导弹，导弹在通关第一关后获得，导弹会同时发射3枚导弹，锁定3个敌人（若不足则只发射对应数量的导弹）</t>
-  </si>
-  <si>
-    <t>玩家可以选择任何一个已经通关过的关卡重新通关，或者无限循环该关卡。如果选择循环，则击败BOSS后就从这关开始重新前进</t>
-  </si>
-  <si>
-    <t>具体配置如下，表格均从第四行开始是实际配置</t>
-  </si>
-  <si>
-    <t>表格名</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>列名</t>
-  </si>
-  <si>
-    <t>用途</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>关卡的id</t>
-  </si>
-  <si>
-    <t>length</t>
-  </si>
-  <si>
-    <t>关卡长度</t>
-  </si>
-  <si>
-    <t>monGroup</t>
-  </si>
-  <si>
-    <t>怪物群id</t>
-  </si>
-  <si>
-    <t>格式为{id|比例，id|比例....}，id为monGroup表的id，比例表示在关卡长度的%多少处出现</t>
-  </si>
-  <si>
-    <t>atkRatio</t>
-  </si>
-  <si>
-    <t>攻击倍率</t>
-  </si>
-  <si>
-    <t>敌方飞行器的器伤害*这个值（向上取整，没有小数）</t>
-  </si>
-  <si>
-    <t>所有倍率，在关卡中由上一关的倍率线性成长到本关倍率。如第一关倍率是1，第二关倍率是10，则10%的长度时是2..以此类推</t>
-  </si>
-  <si>
-    <t>lifeRatio</t>
-  </si>
-  <si>
-    <t>生命倍率</t>
-  </si>
-  <si>
-    <t>敌方飞行器的生命*这个值（向上取整，没有小数）</t>
-  </si>
-  <si>
-    <t>resRatio</t>
-  </si>
-  <si>
-    <t>资源倍率</t>
-  </si>
-  <si>
-    <t>敌方飞行器摧毁时获得的资源乘该值</t>
-  </si>
-  <si>
-    <t>equipment</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>name</t>
   </si>
   <si>
-    <t>武器名</t>
-  </si>
-  <si>
     <t>des</t>
   </si>
   <si>
-    <t>武器说明</t>
-  </si>
-  <si>
-    <t>武器等级</t>
-  </si>
-  <si>
-    <t>dmg</t>
-  </si>
-  <si>
-    <t>武器命中时的伤害</t>
-  </si>
-  <si>
-    <t>cd</t>
-  </si>
-  <si>
-    <t>武器发射需要的时间</t>
+    <t>description</t>
+  </si>
+  <si>
+    <t>timeCostBase</t>
+  </si>
+  <si>
+    <t>timeCostMutiple</t>
   </si>
   <si>
     <t>unlock</t>
   </si>
   <si>
-    <t>对应level表id，通关对应id的关卡后解锁该武器</t>
-  </si>
-  <si>
-    <t>res_1</t>
-  </si>
-  <si>
-    <t>升级该武器需要的资源</t>
-  </si>
-  <si>
-    <t>支持不做修改就能扩展，格式均为res_x。如res_2，res_3就表示第二种，第三种资源。资源为res表的id</t>
-  </si>
-  <si>
-    <t>cost_1</t>
-  </si>
-  <si>
-    <t>升到该等级需要的资源数量</t>
-  </si>
-  <si>
-    <t>支持不做修改就能扩展，格式均为cost_x。如cost_2，cost_3就表示第二种，第三种资源消耗量。与res_x一一对应</t>
-  </si>
-  <si>
     <t>para1</t>
   </si>
   <si>
-    <t>武器的额外参数。具体每个武器再定义，一般可参考des</t>
-  </si>
-  <si>
-    <t>mon</t>
-  </si>
-  <si>
-    <t>敌方飞行器id</t>
-  </si>
-  <si>
-    <t>飞行器描述</t>
-  </si>
-  <si>
-    <t>使用的武器，从equipment表中读出来，逻辑等都使用该武器表的</t>
-  </si>
-  <si>
-    <t>dmgMultiple</t>
-  </si>
-  <si>
-    <t>武器的伤害乘该值，这样计算完后的就是这个飞行器的伤害</t>
-  </si>
-  <si>
-    <t>health</t>
-  </si>
-  <si>
-    <t>飞行器生命</t>
-  </si>
-  <si>
-    <t>res</t>
-  </si>
-  <si>
-    <t>掉落的资源</t>
-  </si>
-  <si>
-    <t>格式为｛id，数量，概率｝，id为res表的id，数量就是掉出来的数量，概率是被击毁时有多大概率掉落该资源</t>
-  </si>
-  <si>
-    <t>size</t>
-  </si>
-  <si>
-    <t>大小</t>
-  </si>
-  <si>
-    <t>战场中占据的格子数</t>
-  </si>
-  <si>
-    <t>敌方飞行器组id</t>
-  </si>
-  <si>
-    <t>飞行器组描述</t>
-  </si>
-  <si>
-    <t>格式为{id1，id2....｝</t>
-  </si>
-  <si>
-    <t>战场从上到下一共是10个格子，这里的id是mon表的id，1-10分别对应10个格子的位置</t>
-  </si>
-  <si>
-    <t>资源id</t>
-  </si>
-  <si>
-    <t>资源名</t>
-  </si>
-  <si>
-    <t>config</t>
-  </si>
-  <si>
-    <t>这个配置的名字</t>
-  </si>
-  <si>
-    <t>配置的描述</t>
-  </si>
-  <si>
-    <t>para_1</t>
-  </si>
-  <si>
-    <t>配置的参数</t>
-  </si>
-  <si>
-    <t>支持可扩展，会以para_1,para_2等方式不断扩张</t>
-  </si>
-  <si>
-    <t>hightech</t>
-  </si>
-  <si>
-    <t>这个高科技的名字</t>
-  </si>
-  <si>
-    <t>高科技的效果</t>
-  </si>
-  <si>
-    <t>timeCostBase</t>
-  </si>
-  <si>
-    <t>升级高科技需要的基础时间</t>
-  </si>
-  <si>
-    <t>timeCostMutiple</t>
-  </si>
-  <si>
-    <t>每次升级后升级时间的乘数。例如1级10秒，这个值为1.2，则2级12秒，3级14秒...四舍五入取整</t>
+    <t>para2</t>
+  </si>
+  <si>
+    <t>这个神器的名字</t>
+  </si>
+  <si>
+    <t>神器的效果</t>
+  </si>
+  <si>
+    <t>界面上的描述</t>
+  </si>
+  <si>
+    <t>升级神器需要的基础时间</t>
+  </si>
+  <si>
+    <t>每次升级后升级时间的乘数。例如1级10秒，这个值为0.2，则2级12秒，3级14秒...四舍五入取整</t>
   </si>
   <si>
     <t>通过第几关后解锁</t>
   </si>
   <si>
-    <t>可变参数，可能有多个，具体效果参看高科技的效果des</t>
+    <t>可变参数，具体效果参看神器的效果des</t>
   </si>
   <si>
     <t>如上</t>
   </si>
   <si>
-    <t>{2|0.1，2|0.2，2|0.3，2|0.4，2|0.5，2|0.6，2|0.7，2|0.8，6|0.9}</t>
-  </si>
-  <si>
-    <t>{2|0.1，5|0.2，2|0.3，5|0.4，2|0.5，5|0.6，2|0.7，5|0.8，6|0.9}</t>
-  </si>
-  <si>
-    <t>{1|0.1，2|0.2，3|0.3，1|0.4，2|0.5，3|0.6，1|0.7，2|0.8，7|0.9}</t>
-  </si>
-  <si>
-    <t>{4|0.1，5|0.2，4|0.3，5|0.4，4|0.5，5|0.6，4|0.7，5|0.8，6|0.9}</t>
-  </si>
-  <si>
-    <t>{1|0.1，2|0.2，3|0.3，4|0.4，5|0.5，1|0.6，2|0.7，3|0.8，7|0.9}</t>
-  </si>
-  <si>
-    <t>{2|0.1，5|0.2，2|0.3，5|0.4，2|0.5，5|0.6，2|0.7，5|0.8，7|0.9}</t>
-  </si>
-  <si>
-    <t>{1|0.1，2|0.2，3|0.3，1|0.4，2|0.5，3|0.6，1|0.7，2|0.8，6|0.9}</t>
-  </si>
-  <si>
-    <t>{4|0.1，5|0.2，4|0.3，5|0.4，4|0.5，5|0.6，4|0.7，5|0.8，7|0.9}</t>
-  </si>
-  <si>
-    <t>{1|0.1，2|0.2，3|0.3，4|0.4，5|0.5，1|0.6，2|0.7，3|0.8，8|0.9}</t>
-  </si>
-  <si>
-    <t>dmgtype</t>
-  </si>
-  <si>
-    <t>res_2</t>
-  </si>
-  <si>
-    <t>cost_2</t>
-  </si>
-  <si>
-    <t>para2</t>
-  </si>
-  <si>
-    <t>para3</t>
-  </si>
-  <si>
-    <t>伤害类型，1为能量，2为物理。</t>
-  </si>
-  <si>
-    <t>对应level表id，通关对应id的关卡后解锁该武器。不填则这行无意义</t>
-  </si>
-  <si>
-    <t>armour</t>
-  </si>
-  <si>
-    <t>这个是飞船的基础生命，如果没了，飞船就会爆炸！然后后退。额外参数para1是生命值，dmgtype表明护甲对这个类型的伤害有减伤</t>
-  </si>
-  <si>
-    <t>shield</t>
-  </si>
-  <si>
-    <t>这个是飞船的基础护盾，护盾会先于护甲被扣除，同时护盾会缓慢恢复。额外参数para1是护盾值，para2是每秒恢复的比例，para3是连续多少秒不受攻击后才开始恢复，被攻击会立即停止恢复，dmgtype表明护盾对这个类型的伤害有减伤</t>
-  </si>
-  <si>
-    <t>laser</t>
-  </si>
-  <si>
-    <t>激光武器，发射一个光束攻击锁定目标，para1是飞行速度/S</t>
-  </si>
-  <si>
-    <t>missile</t>
-  </si>
-  <si>
-    <t>导弹武器，导弹会锁定多个敌人，锁定数量为para1定义。但敌人数量不足则只会发射敌人数量的导弹，不会多发。para2是导弹飞行速度</t>
-  </si>
-  <si>
-    <t>导弹武器，导弹会锁定多个敌人，锁定数量为para1定义。但敌人数量不足则只会发射敌人数量的导弹，不会多发</t>
-  </si>
-  <si>
-    <t>cannon</t>
-  </si>
-  <si>
-    <t>火炮武器，与激光一样，发射一个炮弹攻击锁定目标敌人，para1是飞行速度/S</t>
-  </si>
-  <si>
-    <t>laser_mon</t>
-  </si>
-  <si>
-    <t>missile-mon</t>
-  </si>
-  <si>
-    <t>cannon-mon</t>
-  </si>
-  <si>
-    <t>armourType</t>
-  </si>
-  <si>
-    <t>使用的武器，从equipment表中读出来，逻辑等都使用该武器表的,格式为｛name|数量，name|数量...}</t>
-  </si>
-  <si>
-    <t>护甲类型</t>
-  </si>
-  <si>
-    <t>1为能量，2为物理</t>
-  </si>
-  <si>
-    <t>激光飞船</t>
-  </si>
-  <si>
-    <t>｛laser_mon|1｝</t>
-  </si>
-  <si>
-    <t>{1,10,0.5}</t>
-  </si>
-  <si>
-    <t>火炮飞船</t>
-  </si>
-  <si>
-    <t>｛cannon-mon|1｝</t>
-  </si>
-  <si>
-    <t>激光飞船-弱</t>
-  </si>
-  <si>
-    <t>{1,5,0.2}</t>
-  </si>
-  <si>
-    <t>火炮飞船-弱</t>
-  </si>
-  <si>
-    <t>BOSS-抵抗物理</t>
-  </si>
-  <si>
-    <t>｛laser_mon|2,cannon-mon|2｝</t>
-  </si>
-  <si>
-    <t>{2,1,1}</t>
-  </si>
-  <si>
-    <t>BOSS-抵抗能量</t>
-  </si>
-  <si>
-    <t>战场从上到下一共是10个格子，这里的id是mon表的id，1-10分别对应10个格子的位置，null表示此处无飞船｝</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，1，1，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，2，2，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>基础飞船组</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，1，2，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>激光飞船-弱*6</t>
-  </si>
-  <si>
-    <t>｛null，null，3，3，3，3，3，3，null，null}</t>
-  </si>
-  <si>
-    <t>火炮飞船-弱*6</t>
-  </si>
-  <si>
-    <t>｛null，null，4，4，4，4，4，4，null，null}</t>
-  </si>
-  <si>
-    <t>BOSS飞船-抵抗物理</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，5，null，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>BOSS飞船-抵抗能量</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，6，null，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>BOSS飞船-双BOSS</t>
-  </si>
-  <si>
-    <t>｛null，null，null，5，null，null，6，null，null，null}</t>
-  </si>
-  <si>
-    <t>铁</t>
-  </si>
-  <si>
-    <t>铝</t>
-  </si>
-  <si>
-    <t>startEquip</t>
-  </si>
-  <si>
-    <t>飞船初始具有的装备，格式为name,name，equipment表的名字。默认为1级。</t>
-  </si>
-  <si>
-    <t>armour,laser</t>
-  </si>
-  <si>
-    <t>dmgReduce</t>
-  </si>
-  <si>
-    <t>护甲类型对应时，减少的伤害</t>
-  </si>
-  <si>
-    <t>movement</t>
-  </si>
-  <si>
-    <t>飞船的移动速度，单位是秒</t>
-  </si>
-  <si>
-    <t>autoCollectReduce</t>
-  </si>
-  <si>
-    <t>自动拾取时的损耗</t>
-  </si>
-  <si>
-    <t>backRange</t>
-  </si>
-  <si>
-    <t>死亡时后退距离</t>
-  </si>
-  <si>
-    <t>hightechLimit</t>
-  </si>
-  <si>
-    <t>同时研发的高科技数量</t>
-  </si>
-  <si>
-    <t>offlineMax</t>
-  </si>
-  <si>
-    <t>离线时长(h）</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>这个神器的名字</t>
-  </si>
-  <si>
-    <t>神器的效果</t>
-  </si>
-  <si>
-    <t>界面上的描述</t>
-  </si>
-  <si>
-    <t>升级神器需要的基础时间</t>
-  </si>
-  <si>
-    <t>每次升级后升级时间的乘数。例如1级10秒，这个值为0.2，则2级12秒，3级14秒...四舍五入取整</t>
-  </si>
-  <si>
-    <t>可变参数，具体效果参看神器的效果des</t>
-  </si>
-  <si>
     <t>超时空炼铁炉</t>
   </si>
   <si>
@@ -562,19 +89,19 @@
     <t>正电子聚焦装置</t>
   </si>
   <si>
-    <t>提高所有能量武器的伤害，效果为原伤害*（1+para1*等级）向上取整.</t>
-  </si>
-  <si>
-    <t>能量武器伤害提高{para1*等级}</t>
+    <t>提高所有武器的伤害，效果为原伤害*（1+para1)^等级向上取整.</t>
+  </si>
+  <si>
+    <t>所有武器伤害提高{(1+para1)^等级,百分比显示,保留两位小数,即100.3%展示为100%}</t>
   </si>
   <si>
     <t>简并态装甲</t>
   </si>
   <si>
-    <t>armour当前值增加（1+para1*等级），向上取整。</t>
-  </si>
-  <si>
-    <t>生命增加{para1*等级}</t>
+    <t>生命和护盾最大值增加（1+para1）^等级，向上取整。</t>
+  </si>
+  <si>
+    <t>生命增加{（1+para1）^等级,百分比显示,保留两位小数,即100.3%展示为100%}</t>
   </si>
 </sst>
 </file>
@@ -1190,18 +717,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1511,102 +1032,102 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="16.4444444444444" customWidth="1"/>
+    <col min="1" max="1" width="16.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>165</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>99</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>166</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>167</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>168</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>170</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>84</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>171</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>171</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>172</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>173</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>18</v>
       </c>
       <c r="D4">
         <v>60</v>
@@ -1615,7 +1136,7 @@
         <v>0.2</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
         <v>30</v>
@@ -1626,13 +1147,13 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>175</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>177</v>
+        <v>21</v>
       </c>
       <c r="D5">
         <v>60</v>
@@ -1641,7 +1162,7 @@
         <v>0.2</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G5">
         <v>0.1</v>
@@ -1649,13 +1170,13 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>178</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>179</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>180</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>60</v>
@@ -1664,10 +1185,10 @@
         <v>0.2</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/space-battleship/config_excel/hightech.xlsx
+++ b/space-battleship/config_excel/hightech.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\放置\space-battleship\config_excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="hightech" sheetId="8" r:id="rId1"/>
@@ -1036,9 +1041,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="16.4416666666667" customWidth="1"/>
+    <col min="1" max="1" width="16.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1185,7 +1190,7 @@
         <v>0.2</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6">
         <v>0.1</v>

--- a/space-battleship/config_excel/hightech.xlsx
+++ b/space-battleship/config_excel/hightech.xlsx
@@ -3,13 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\放置\space-battleship\config_excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="hightech" sheetId="8" r:id="rId1"/>
@@ -43,10 +38,10 @@
     <t>description</t>
   </si>
   <si>
-    <t>timeCostBase</t>
-  </si>
-  <si>
-    <t>timeCostMutiple</t>
+    <t>tpCostBase</t>
+  </si>
+  <si>
+    <t>tpCostMutiple</t>
   </si>
   <si>
     <t>unlock</t>
@@ -67,10 +62,10 @@
     <t>界面上的描述</t>
   </si>
   <si>
-    <t>升级神器需要的基础时间</t>
-  </si>
-  <si>
-    <t>每次升级后升级时间的乘数。例如1级10秒，这个值为0.2，则2级12秒，3级14秒...四舍五入取整</t>
+    <t>升级高科技需要的基础时间</t>
+  </si>
+  <si>
+    <t>每次升级后升级时间的乘数。tpCostBase*(1+tpCostMutiple*等级),四舍五入</t>
   </si>
   <si>
     <t>通过第几关后解锁</t>
@@ -1041,9 +1036,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="16.4444444444444" customWidth="1"/>
+    <col min="1" max="1" width="16.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1135,7 +1130,7 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>0.2</v>
@@ -1161,7 +1156,7 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E5">
         <v>0.2</v>
@@ -1184,7 +1179,7 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E6">
         <v>0.2</v>

--- a/space-battleship/config_excel/hightech.xlsx
+++ b/space-battleship/config_excel/hightech.xlsx
@@ -1130,7 +1130,7 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="E4">
         <v>0.2</v>
@@ -1142,7 +1142,7 @@
         <v>30</v>
       </c>
       <c r="H4">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1156,7 +1156,7 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="E5">
         <v>0.2</v>
@@ -1165,7 +1165,7 @@
         <v>4</v>
       </c>
       <c r="G5">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1179,7 +1179,7 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="E6">
         <v>0.2</v>
@@ -1188,7 +1188,7 @@
         <v>4</v>
       </c>
       <c r="G6">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>

--- a/space-battleship/config_excel/hightech.xlsx
+++ b/space-battleship/config_excel/hightech.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
   <si>
     <t>name</t>
   </si>
@@ -83,7 +83,7 @@
     <t>每para1秒在屏幕中生成一个铁块，总共含有根据过去一分钟的铁生成量*para2*等级的铁，向上取整，点击获取，10秒后消失</t>
   </si>
   <si>
-    <t>每para1秒在屏幕中生成一个含有{过去一分钟的铁生成量*para2*等级,向上取整,不含自身}的铁块</t>
+    <t>每para1秒在屏幕中生成一个含有{过去一分钟的铁生成量*para2*等级,向上取整,不含自身}的铁的铁块</t>
   </si>
   <si>
     <t>正电子聚焦装置</t>
@@ -102,6 +102,15 @@
   </si>
   <si>
     <t>生命增加{（1+para1）^等级,百分比显示,保留两位小数,即100.3%展示为100%}</t>
+  </si>
+  <si>
+    <t>宝石熔炼炉</t>
+  </si>
+  <si>
+    <t>每para1秒在屏幕中生成一个宝石核心，总共含有根据过去一分钟的宝石碎片生成量*para2*等级的碎片，向上取整，鼠标划过获取，10秒后消失</t>
+  </si>
+  <si>
+    <t>每para1秒在屏幕中生成一个含有{过去一分钟的宝石碎片生成量*para2*等级,向上取整,不含自身}的宝石碎片的宝石核心块</t>
   </si>
 </sst>
 </file>
@@ -1035,8 +1044,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="7"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="16.4416666666667" customWidth="1"/>
   </cols>
@@ -1057,9 +1066,6 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
       <c r="G1" t="s">
         <v>6</v>
       </c>
@@ -1083,9 +1089,6 @@
       <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
       <c r="G2" t="s">
         <v>14</v>
       </c>
@@ -1109,9 +1112,6 @@
       <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
       <c r="G3" t="s">
         <v>15</v>
       </c>
@@ -1135,9 +1135,6 @@
       <c r="E4">
         <v>0.2</v>
       </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
       <c r="G4" s="1">
         <v>30</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="E5">
         <v>0.2</v>
       </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
       <c r="G5">
         <v>0.05</v>
       </c>
@@ -1184,11 +1178,31 @@
       <c r="E6">
         <v>0.2</v>
       </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
       <c r="G6">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7">
+        <v>60</v>
+      </c>
+      <c r="E7">
+        <v>0.05</v>
+      </c>
+      <c r="G7" s="1">
+        <v>20</v>
+      </c>
+      <c r="H7">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/space-battleship/config_excel/hightech.xlsx
+++ b/space-battleship/config_excel/hightech.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>name</t>
   </si>
@@ -44,9 +44,6 @@
     <t>tpCostMutiple</t>
   </si>
   <si>
-    <t>unlock</t>
-  </si>
-  <si>
     <t>para1</t>
   </si>
   <si>
@@ -66,9 +63,6 @@
   </si>
   <si>
     <t>每次升级后升级时间的乘数。tpCostBase*(1+tpCostMutiple*等级),四舍五入</t>
-  </si>
-  <si>
-    <t>通过第几关后解锁</t>
   </si>
   <si>
     <t>可变参数，具体效果参看神器的效果des</t>
@@ -1067,67 +1061,67 @@
         <v>4</v>
       </c>
       <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
         <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
       </c>
       <c r="D4">
         <v>60</v>
@@ -1144,13 +1138,13 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
         <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
       </c>
       <c r="D5">
         <v>60</v>
@@ -1164,13 +1158,13 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
         <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
       </c>
       <c r="D6">
         <v>60</v>
@@ -1184,25 +1178,25 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
         <v>25</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
       </c>
       <c r="D7">
         <v>60</v>
       </c>
       <c r="E7">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="G7" s="1">
         <v>20</v>
       </c>
       <c r="H7">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>

--- a/space-battleship/config_excel/hightech.xlsx
+++ b/space-battleship/config_excel/hightech.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\放置\space-battleship\config_excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="hightech" sheetId="8" r:id="rId1"/>
@@ -1039,9 +1044,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="16.4416666666667" customWidth="1"/>
+    <col min="1" max="1" width="16.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="18.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="26.5555555555556" customWidth="1"/>
+    <col min="8" max="8" width="10.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1127,7 +1135,7 @@
         <v>60</v>
       </c>
       <c r="E4">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
         <v>30</v>
@@ -1150,7 +1158,7 @@
         <v>60</v>
       </c>
       <c r="E5">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="G5">
         <v>0.05</v>
@@ -1170,7 +1178,7 @@
         <v>60</v>
       </c>
       <c r="E6">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>0.05</v>
@@ -1190,7 +1198,7 @@
         <v>60</v>
       </c>
       <c r="E7">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
         <v>20</v>

--- a/space-battleship/config_excel/hightech.xlsx
+++ b/space-battleship/config_excel/hightech.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
   <si>
     <t>name</t>
   </si>
@@ -49,6 +49,9 @@
     <t>tpCostMutiple</t>
   </si>
   <si>
+    <t>tpCostMutiple2</t>
+  </si>
+  <si>
     <t>para1</t>
   </si>
   <si>
@@ -74,6 +77,9 @@
   </si>
   <si>
     <t>如上</t>
+  </si>
+  <si>
+    <t>400级开始启用,公式改为tpCostBase*(1+tpCostMutiple*等级)*(1+tpCostMutiple2)^(LV-400)</t>
   </si>
   <si>
     <t>超时空炼铁炉</t>
@@ -1068,74 +1074,86 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4">
         <v>60</v>
       </c>
       <c r="E4">
         <v>2</v>
+      </c>
+      <c r="F4">
+        <v>0.1</v>
       </c>
       <c r="G4" s="1">
         <v>30</v>
@@ -1146,19 +1164,22 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5">
         <v>60</v>
       </c>
       <c r="E5">
         <v>2</v>
+      </c>
+      <c r="F5">
+        <v>0.1</v>
       </c>
       <c r="G5">
         <v>0.05</v>
@@ -1166,19 +1187,22 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>60</v>
       </c>
       <c r="E6">
         <v>2</v>
+      </c>
+      <c r="F6">
+        <v>0.1</v>
       </c>
       <c r="G6">
         <v>0.05</v>
@@ -1186,19 +1210,22 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7">
         <v>60</v>
       </c>
       <c r="E7">
         <v>2</v>
+      </c>
+      <c r="F7">
+        <v>0.1</v>
       </c>
       <c r="G7" s="1">
         <v>20</v>

--- a/space-battleship/config_excel/hightech.xlsx
+++ b/space-battleship/config_excel/hightech.xlsx
@@ -1212,11 +1212,15 @@
       <c r="A7" t="s">
         <v>25</v>
       </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
+      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B7" t="inlineStr">
+        <is>
+          <t>每para1秒在屏幕中生成一个强化核心，总共含有根据过去一分钟的强化碎片生成量*para2*等级的碎片，向上取整，鼠标划过获取，10秒后消失</t>
+        </is>
+      </c>
+      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="C7" t="inlineStr">
+        <is>
+          <t>每para1秒在屏幕中生成一个含有{过去一分钟的宝石碎片生成量*para2*等级,向上取整,不含自身}的强化核心块</t>
+        </is>
       </c>
       <c r="D7">
         <v>60</v>
